--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6EA4AFA-C1E2-B942-93FC-D425C57935E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C97202-96DB-C344-A648-57BC22D6D613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
@@ -853,7 +853,7 @@
         <v>28</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>38</v>

--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C97202-96DB-C344-A648-57BC22D6D613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0303D3-AAD3-8E45-A07C-32524AC30C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="2800" yWindow="600" windowWidth="29400" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -226,6 +229,22 @@
   </si>
   <si>
     <t>已完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在聊天界面自己的气泡加时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际完成时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>撤回消息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本未更新时不允许访问</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -285,7 +304,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -308,13 +327,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -348,7 +380,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -744,7 +791,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-  <dimension ref="A1:K15"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="29.83203125" style="1" customWidth="1"/>
@@ -752,9 +800,10 @@
     <col min="4" max="5" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="11" max="11" width="12.5" customWidth="1"/>
+    <col min="12" max="12" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -788,8 +837,11 @@
       <c r="K1" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="34">
+      <c r="L1" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="34" hidden="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -824,8 +876,11 @@
       <c r="K2" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="34">
+      <c r="L2" s="12">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="34" hidden="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -843,7 +898,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G14" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G17" si="0">F3-E3</f>
         <v>-8</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -858,8 +913,11 @@
       <c r="K3" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="34">
+      <c r="L3" s="12">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="34">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -892,8 +950,9 @@
       <c r="K4" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="17">
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="17">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -928,8 +987,9 @@
       <c r="K5" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="51">
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="51" hidden="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -962,8 +1022,9 @@
         <v>30</v>
       </c>
       <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" ht="34">
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="34">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -996,8 +1057,9 @@
       <c r="K7" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="34">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" ht="34">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1030,8 +1092,9 @@
       <c r="K8" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="17">
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="17" hidden="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1062,8 +1125,9 @@
         <v>30</v>
       </c>
       <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="68">
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="68">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1098,8 +1162,9 @@
       <c r="K10" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="34">
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="34">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1134,8 +1199,9 @@
       <c r="K11" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="34">
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" ht="34" hidden="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1166,8 +1232,9 @@
         <v>30</v>
       </c>
       <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" ht="17">
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" ht="17" hidden="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1200,56 +1267,184 @@
       <c r="K13" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" s="7" customFormat="1">
-      <c r="A14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="6">
-        <f>SUM(E2:E13)</f>
-        <v>633.20000000000005</v>
-      </c>
-      <c r="F14" s="4">
-        <f>SUM(F2:F13)</f>
-        <v>557</v>
+      <c r="L13" s="12">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="17">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
       </c>
       <c r="G14" s="2">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" ht="17" hidden="1">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2">
+        <v>30</v>
+      </c>
+      <c r="G15" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" ht="17">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" s="7" customFormat="1" hidden="1">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="6">
+        <f>SUM(E2:E16)</f>
+        <v>663.2</v>
+      </c>
+      <c r="F17" s="4">
+        <f>SUM(F2:F16)</f>
+        <v>587</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" si="0"/>
         <v>-76.200000000000045</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10">
-        <f>F14-SUMIF(I2:I12,"已支付",F2:F12)</f>
-        <v>350</v>
-      </c>
-      <c r="K14" s="10"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="H15" s="10" t="s">
+      <c r="I17" s="9"/>
+      <c r="J17" s="10">
+        <f>F17-SUMIF(I2:I12,"已支付",F2:F12)</f>
+        <v>380</v>
+      </c>
+      <c r="K17" s="10"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" hidden="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="10">
+      <c r="I18" s="16"/>
+      <c r="J18" s="15">
         <f>SUMIF(I2:I12,"已支付",F2:F12)</f>
         <v>207</v>
       </c>
-      <c r="K15" s="10"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L18" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="已支付"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="未完成"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
@@ -1268,7 +1463,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I13 J14 I16:I1048576">
+  <conditionalFormatting sqref="I1:I16 J17 I19:I1048576">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"已支付"</formula>
     </cfRule>

--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0303D3-AAD3-8E45-A07C-32524AC30C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32737BDC-45B5-3049-96C4-3384E6D16B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="600" windowWidth="29400" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$20</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -245,6 +245,26 @@
   </si>
   <si>
     <t>版本未更新时不允许访问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单处理的聊天按钮或员工端的联系管理员按钮上有新消息未读时显示红点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月5日前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在左侧边栏加入需要已读类型的通知中心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月6日前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要显示红点、使用单独的页面进行呈现。显示各种状态更新以及聊天消息。每个通知点击进去都能跳转到对应的功能区并打开该模块。其次右上角把铃铛改成显示这种类型消息的，并且支持一件已读。其次现在原有的未完成任务铃铛图标改成其他的。已读一条消息就减少红点哦。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -346,7 +366,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -371,6 +391,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -379,18 +402,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -791,8 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="29.83203125" style="1" customWidth="1"/>
@@ -837,11 +847,11 @@
       <c r="K1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" hidden="1">
+    <row r="2" spans="1:12" ht="34">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -876,11 +886,11 @@
       <c r="K2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="8">
         <v>46176</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="34" hidden="1">
+    <row r="3" spans="1:12" ht="34">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -898,7 +908,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G17" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G19" si="0">F3-E3</f>
         <v>-8</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -913,7 +923,7 @@
       <c r="K3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="8">
         <v>46176</v>
       </c>
     </row>
@@ -945,12 +955,14 @@
         <v>28</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L4" s="2"/>
+      <c r="L4" s="8">
+        <v>46177</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="17">
       <c r="A5" s="2">
@@ -982,14 +994,16 @@
         <v>28</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" ht="51" hidden="1">
+      <c r="L5" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="51">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1052,12 +1066,14 @@
         <v>28</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="2"/>
+      <c r="L7" s="8">
+        <v>46177</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="34">
       <c r="A8" s="2">
@@ -1087,14 +1103,16 @@
         <v>28</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" ht="17" hidden="1">
+      <c r="L8" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1147,7 +1165,7 @@
         <v>39</v>
       </c>
       <c r="G10" s="2">
-        <f>F10-E10</f>
+        <f t="shared" si="0"/>
         <v>-11</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -1157,12 +1175,14 @@
         <v>28</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L10" s="2"/>
+      <c r="L10" s="8">
+        <v>46177</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="34">
       <c r="A11" s="2">
@@ -1194,14 +1214,16 @@
         <v>28</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" ht="34" hidden="1">
+      <c r="L11" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="34">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1234,7 +1256,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="17" hidden="1">
+    <row r="13" spans="1:12" ht="17">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1267,7 +1289,7 @@
       <c r="K13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="8">
         <v>46176</v>
       </c>
     </row>
@@ -1299,14 +1321,16 @@
         <v>28</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" ht="17" hidden="1">
+      <c r="L14" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1359,6 +1383,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -1368,83 +1393,142 @@
         <v>28</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" s="7" customFormat="1" hidden="1">
-      <c r="A17" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="6">
-        <f>SUM(E2:E16)</f>
-        <v>663.2</v>
-      </c>
-      <c r="F17" s="4">
-        <f>SUM(F2:F16)</f>
-        <v>587</v>
+      <c r="L16" s="8">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="51">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
       </c>
       <c r="G17" s="2">
         <f t="shared" si="0"/>
-        <v>-76.200000000000045</v>
-      </c>
-      <c r="H17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="153">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="2">
+        <v>60</v>
+      </c>
+      <c r="F18" s="2">
+        <v>50</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="0"/>
+        <v>-10</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="8">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="7" customFormat="1">
+      <c r="A19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="6">
+        <f>SUM(E2:E18)</f>
+        <v>723.2</v>
+      </c>
+      <c r="F19" s="4">
+        <f>SUM(F2:F18)</f>
+        <v>637</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="0"/>
+        <v>-86.200000000000045</v>
+      </c>
+      <c r="H19" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10">
-        <f>F17-SUMIF(I2:I12,"已支付",F2:F12)</f>
-        <v>380</v>
-      </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="5"/>
-    </row>
-    <row r="18" spans="1:12" hidden="1">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="15" t="s">
+      <c r="I19" s="10"/>
+      <c r="J19" s="11">
+        <f>F19-SUMIF(I2:I12,"已支付",F2:F12)</f>
+        <v>430</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="H20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="16"/>
-      <c r="J18" s="15">
+      <c r="I20" s="13"/>
+      <c r="J20" s="12">
         <f>SUMIF(I2:I12,"已支付",F2:F12)</f>
         <v>207</v>
       </c>
-      <c r="K18" s="15"/>
-      <c r="L18" s="13"/>
+      <c r="K20" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L18" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="已支付"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="未完成"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L20" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}"/>
   <mergeCells count="5">
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="J20:K20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
@@ -1463,7 +1547,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I16 J17 I19:I1048576">
+  <conditionalFormatting sqref="I1:I18 J19 I21:I1048576">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"已支付"</formula>
     </cfRule>
@@ -1477,5 +1561,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32737BDC-45B5-3049-96C4-3384E6D16B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F8F2EB-9BB3-9949-9FBB-0A791C48238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="300" yWindow="900" windowWidth="28800" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>订单处理详情发送图片功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>订单信息修改功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,6 +261,22 @@
   </si>
   <si>
     <t>需要显示红点、使用单独的页面进行呈现。显示各种状态更新以及聊天消息。每个通知点击进去都能跳转到对应的功能区并打开该模块。其次右上角把铃铛改成显示这种类型消息的，并且支持一件已读。其次现在原有的未完成任务铃铛图标改成其他的。已读一条消息就减少红点哦。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>模板支持上传图片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加入一键下载图片功能，模板配置中支持图像上传表单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单处理详情聊天发送图片功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6月12日前</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -802,7 +814,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-  <dimension ref="A1:L20"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="29.83203125" style="1" customWidth="1"/>
@@ -827,31 +840,31 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="G1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="K1" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="34">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="34" hidden="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -862,7 +875,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2">
         <v>43.2</v>
@@ -875,22 +888,22 @@
         <v>-28.200000000000003</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L2" s="8">
         <v>46176</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="34">
+    <row r="3" spans="1:12" ht="34" hidden="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -899,7 +912,7 @@
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2">
         <v>60</v>
@@ -908,26 +921,26 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G19" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G20" si="0">F3-E3</f>
         <v>-8</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L3" s="8">
         <v>46176</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="34">
+    <row r="4" spans="1:12" ht="34" hidden="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -936,7 +949,7 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2">
         <v>0</v>
@@ -949,22 +962,22 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L4" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17">
+    <row r="5" spans="1:12" ht="17" hidden="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -975,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2">
         <v>80</v>
@@ -988,22 +1001,22 @@
         <v>-18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L5" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="51">
+    <row r="6" spans="1:12" ht="51" hidden="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1011,10 +1024,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2">
         <v>70</v>
@@ -1027,18 +1040,18 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="34">
+    <row r="7" spans="1:12" ht="34" hidden="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1047,7 +1060,7 @@
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2">
         <v>0</v>
@@ -1060,22 +1073,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L7" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="34">
+    <row r="8" spans="1:12" ht="34" hidden="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1084,7 +1097,7 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2">
         <v>0</v>
@@ -1097,31 +1110,31 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17">
+    <row r="9" spans="1:12" ht="17" hidden="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2">
         <v>180</v>
@@ -1134,29 +1147,29 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="68">
+    <row r="10" spans="1:12" ht="68" hidden="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2">
         <v>50</v>
@@ -1169,33 +1182,33 @@
         <v>-11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L10" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="34">
+    <row r="11" spans="1:12" ht="34" hidden="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2">
         <v>50</v>
@@ -1208,31 +1221,31 @@
         <v>-11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L11" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="34">
+    <row r="12" spans="1:12" ht="34" hidden="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2">
         <v>100</v>
@@ -1245,27 +1258,27 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="17">
+    <row r="13" spans="1:12" ht="17" hidden="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1278,31 +1291,31 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L13" s="8">
         <v>46176</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17">
+    <row r="14" spans="1:12" ht="17" hidden="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -1315,31 +1328,31 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L14" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17">
+    <row r="15" spans="1:12" ht="17" hidden="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2">
         <v>30</v>
@@ -1352,29 +1365,29 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="K15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="17">
+    <row r="16" spans="1:12" ht="17" hidden="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2">
         <v>0</v>
@@ -1387,31 +1400,31 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L16" s="8">
         <v>46177</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="51">
+    <row r="17" spans="1:12" ht="51" hidden="1">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3"/>
       <c r="D17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E17" s="2">
         <v>0</v>
@@ -1424,33 +1437,33 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L17" s="8">
         <v>46178</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="153">
+    <row r="18" spans="1:12" ht="153" hidden="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2">
         <v>60</v>
@@ -1463,72 +1476,120 @@
         <v>-10</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L18" s="8">
         <v>46178</v>
       </c>
     </row>
-    <row r="19" spans="1:12" s="7" customFormat="1">
-      <c r="A19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="6">
-        <f>SUM(E2:E18)</f>
-        <v>723.2</v>
-      </c>
-      <c r="F19" s="4">
-        <f>SUM(F2:F18)</f>
-        <v>637</v>
+    <row r="19" spans="1:12" ht="34">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2">
+        <v>170</v>
+      </c>
+      <c r="F19" s="2">
+        <v>130</v>
       </c>
       <c r="G19" s="2">
         <f t="shared" si="0"/>
-        <v>-86.200000000000045</v>
-      </c>
-      <c r="H19" s="10" t="s">
+        <v>-40</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" s="7" customFormat="1" hidden="1">
+      <c r="A20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="11">
-        <f>F19-SUMIF(I2:I12,"已支付",F2:F12)</f>
-        <v>430</v>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="5"/>
-    </row>
-    <row r="20" spans="1:12">
-      <c r="H20" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="12">
+      <c r="E20" s="6">
+        <f>SUM(E2:E19)</f>
+        <v>893.2</v>
+      </c>
+      <c r="F20" s="4">
+        <f>SUM(F2:F19)</f>
+        <v>767</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>-126.20000000000005</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="11">
+        <f>F20-SUMIF(I2:I12,"已支付",F2:F12)</f>
+        <v>560</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" hidden="1">
+      <c r="H21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="13"/>
+      <c r="J21" s="12">
         <f>SUMIF(I2:I12,"已支付",F2:F12)</f>
         <v>207</v>
       </c>
-      <c r="K20" s="12"/>
+      <c r="K21" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L20" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}"/>
+  <autoFilter ref="A1:L21" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="已支付"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="未完成"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="H20:I20"/>
     <mergeCell ref="J20:K20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="J21:K21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
@@ -1547,7 +1608,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I18 J19 I21:I1048576">
+  <conditionalFormatting sqref="I1:I19 J20 I22:I1048576">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"已支付"</formula>
     </cfRule>

--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F8F2EB-9BB3-9949-9FBB-0A791C48238D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59F1A8F-F1DA-4C4E-BF1B-98083C3450FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="300" yWindow="900" windowWidth="28800" windowHeight="16960" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="61">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -277,6 +277,10 @@
   </si>
   <si>
     <t>6月12日前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>员工订单历史界面支持筛选内部字段值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -814,8 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="29.83203125" style="1" customWidth="1"/>
@@ -864,7 +867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34" hidden="1">
+    <row r="2" spans="1:12" ht="34">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -903,7 +906,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="34" hidden="1">
+    <row r="3" spans="1:12" ht="34">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -921,7 +924,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G20" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G22" si="0">F3-E3</f>
         <v>-8</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -940,7 +943,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="34" hidden="1">
+    <row r="4" spans="1:12" ht="34">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -977,7 +980,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17" hidden="1">
+    <row r="5" spans="1:12" ht="17">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1016,7 +1019,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="51" hidden="1">
+    <row r="6" spans="1:12" ht="51">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1051,7 +1054,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="34" hidden="1">
+    <row r="7" spans="1:12" ht="34">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1088,7 +1091,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="34" hidden="1">
+    <row r="8" spans="1:12" ht="34">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17" hidden="1">
+    <row r="9" spans="1:12" ht="17">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1158,7 +1161,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="68" hidden="1">
+    <row r="10" spans="1:12" ht="68">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="34" hidden="1">
+    <row r="11" spans="1:12" ht="34">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="34" hidden="1">
+    <row r="12" spans="1:12" ht="34">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1269,7 +1272,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="17" hidden="1">
+    <row r="13" spans="1:12" ht="17">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1306,7 +1309,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17" hidden="1">
+    <row r="14" spans="1:12" ht="17">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1343,7 +1346,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" hidden="1">
+    <row r="15" spans="1:12" ht="17">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1378,7 +1381,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="17" hidden="1">
+    <row r="16" spans="1:12" ht="17">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="51" hidden="1">
+    <row r="17" spans="1:12" ht="51">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1452,7 +1455,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="153" hidden="1">
+    <row r="18" spans="1:12" ht="153">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1521,75 +1524,113 @@
         <v>27</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>59</v>
       </c>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" s="7" customFormat="1" hidden="1">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:12" ht="34">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12" s="7" customFormat="1">
+      <c r="A22" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="5" t="s">
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="6">
-        <f>SUM(E2:E19)</f>
+      <c r="E22" s="6">
+        <f>SUM(E2:E20)</f>
         <v>893.2</v>
       </c>
-      <c r="F20" s="4">
-        <f>SUM(F2:F19)</f>
+      <c r="F22" s="4">
+        <f>SUM(F2:F20)</f>
         <v>767</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G22" s="2">
         <f t="shared" si="0"/>
         <v>-126.20000000000005</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H22" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="11">
-        <f>F20-SUMIF(I2:I12,"已支付",F2:F12)</f>
-        <v>560</v>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="5"/>
-    </row>
-    <row r="21" spans="1:12" hidden="1">
-      <c r="H21" s="12" t="s">
+      <c r="I22" s="10"/>
+      <c r="J22" s="11">
+        <f>F22-SUMIF(I2:I21,"已支付",F2:F21)</f>
+        <v>380</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="H23" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="12">
-        <f>SUMIF(I2:I12,"已支付",F2:F12)</f>
-        <v>207</v>
-      </c>
-      <c r="K21" s="12"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="12">
+        <f>SUMIF(I2:I21,"已支付",F2:F21)</f>
+        <v>387</v>
+      </c>
+      <c r="K23" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L21" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-    <filterColumn colId="8">
-      <filters>
-        <filter val="已支付"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="未完成"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L23" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}"/>
   <mergeCells count="5">
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="J23:K23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
@@ -1608,7 +1649,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I19 J20 I22:I1048576">
+  <conditionalFormatting sqref="I1:I21 J22 I24:I1048576">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"已支付"</formula>
     </cfRule>

--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59F1A8F-F1DA-4C4E-BF1B-98083C3450FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42195A2E-B66E-5248-A4C8-34E080529518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26720" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1559,12 +1559,14 @@
         <v>27</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L20" s="8"/>
+      <c r="L20" s="8">
+        <v>46181</v>
+      </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="2"/>

--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42195A2E-B66E-5248-A4C8-34E080529518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F48BEE3-76C0-184B-B453-4F1B5ACC25ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19520" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="75">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -281,6 +281,61 @@
   </si>
   <si>
     <t>员工订单历史界面支持筛选内部字段值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复订单修改后余额再次扣除的bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复公告权限问题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公告权限为不可查看时仍然可以在左侧边栏找到进入入口与查看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强调弹窗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在App模板配置中支持配置“强调弹窗”配置，该配置需要需要你选择你在当前模板配置中设置的字段进行多选来选择需要展示的字段与字段值，配置弹窗时，需要配置触发条件，设置触发字段，并且需要你填写字段匹配值，比如说你可以选择多个字段然后每个字段可以配置多个匹配值，当这些条件同时满足（包含）时，弹窗将会弹出。</t>
+  </si>
+  <si>
+    <t>6月10日之前</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>App模版编辑器支持上传多张图片， 支持多张一键导出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工单处理部分的“查看/回复”按钮支持显示红点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>看到就消失。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账户组订单查看权限新增“下属订单”，“其他订单”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账户组工单处理的查看权限新增“下属工单”，“其他工单”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仪表盘默认显示所有下属创建的订单或工单数据或用户</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>订单填写表单上传图片组件存在问题，单独给一个上传会导致给当前表单下所有的图片上传器共用文件，模板中出现多个图片上传器在上传时会出现该问题。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -818,7 +873,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
-  <dimension ref="A1:L23"/>
+  <sheetPr filterMode="1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="29.83203125" style="1" customWidth="1"/>
@@ -867,7 +925,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="34">
+    <row r="2" spans="1:12" ht="34" hidden="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -906,7 +964,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="34">
+    <row r="3" spans="1:12" ht="34" hidden="1">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -924,7 +982,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G22" si="0">F3-E3</f>
+        <f t="shared" ref="G3:G31" si="0">F3-E3</f>
         <v>-8</v>
       </c>
       <c r="H3" s="2" t="s">
@@ -943,7 +1001,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="34">
+    <row r="4" spans="1:12" ht="34" hidden="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -980,7 +1038,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17">
+    <row r="5" spans="1:12" ht="17" hidden="1">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1019,7 +1077,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="51">
+    <row r="6" spans="1:12" ht="51" hidden="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1054,7 +1112,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="34">
+    <row r="7" spans="1:12" ht="34" hidden="1">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1091,7 +1149,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="34">
+    <row r="8" spans="1:12" ht="34" hidden="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1128,7 +1186,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17">
+    <row r="9" spans="1:12" ht="17" hidden="1">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1161,7 +1219,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="68">
+    <row r="10" spans="1:12" ht="68" hidden="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1200,7 +1258,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="34">
+    <row r="11" spans="1:12" ht="34" hidden="1">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1239,7 +1297,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="34">
+    <row r="12" spans="1:12" ht="34" hidden="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1272,7 +1330,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" ht="17">
+    <row r="13" spans="1:12" ht="17" hidden="1">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1309,7 +1367,7 @@
         <v>46176</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17">
+    <row r="14" spans="1:12" ht="17" hidden="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1346,7 +1404,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17">
+    <row r="15" spans="1:12" ht="17" hidden="1">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1381,7 +1439,7 @@
       </c>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" ht="17">
+    <row r="16" spans="1:12" ht="17" hidden="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1418,7 +1476,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="51">
+    <row r="17" spans="1:12" ht="51" hidden="1">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1455,7 +1513,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="153">
+    <row r="18" spans="1:12" ht="153" hidden="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1494,7 +1552,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="34">
+    <row r="19" spans="1:12" ht="34" hidden="1">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1531,7 +1589,7 @@
       </c>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="34">
+    <row r="20" spans="1:12" ht="34" hidden="1">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1568,71 +1626,411 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
+    <row r="21" spans="1:12" ht="34" hidden="1">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>61</v>
+      </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="8"/>
-    </row>
-    <row r="22" spans="1:12" s="7" customFormat="1">
-      <c r="A22" s="9" t="s">
+      <c r="D21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="8">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="74" hidden="1" customHeight="1">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="8">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="212" customHeight="1">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="2">
+        <v>90</v>
+      </c>
+      <c r="F23" s="2">
+        <f>90*0.63</f>
+        <v>56.7</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="0"/>
+        <v>-33.299999999999997</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" ht="51" customHeight="1">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="3"/>
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2">
+        <v>30</v>
+      </c>
+      <c r="F24" s="2">
+        <f>30*0.63</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="0"/>
+        <v>-11.100000000000001</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" ht="51" customHeight="1">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" ht="51" customHeight="1">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2">
+        <v>30</v>
+      </c>
+      <c r="F26" s="2">
+        <f>30*0.63</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="0"/>
+        <v>-11.100000000000001</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12" ht="51" customHeight="1">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="3"/>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2">
+        <v>30</v>
+      </c>
+      <c r="F27" s="2">
+        <f>30*0.63</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="G27" s="2">
+        <f>F27-E27</f>
+        <v>-11.100000000000001</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" ht="51" customHeight="1">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2">
+        <v>18</v>
+      </c>
+      <c r="F28" s="2">
+        <v>12.34</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" ref="G28:G29" si="1">F28-E28</f>
+        <v>-5.66</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="8"/>
+    </row>
+    <row r="29" spans="1:12" ht="85">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="2">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" s="7" customFormat="1" hidden="1">
+      <c r="A31" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="5" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="6">
-        <f>SUM(E2:E20)</f>
-        <v>893.2</v>
-      </c>
-      <c r="F22" s="4">
-        <f>SUM(F2:F20)</f>
-        <v>767</v>
-      </c>
-      <c r="G22" s="2">
-        <f t="shared" si="0"/>
-        <v>-126.20000000000005</v>
-      </c>
-      <c r="H22" s="10" t="s">
+      <c r="E31" s="6">
+        <f>SUM(E2:E29)</f>
+        <v>1091.2</v>
+      </c>
+      <c r="F31" s="4">
+        <f>SUM(F2:F28)</f>
+        <v>892.74</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="0"/>
+        <v>-198.46000000000004</v>
+      </c>
+      <c r="H31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="11">
-        <f>F22-SUMIF(I2:I21,"已支付",F2:F21)</f>
-        <v>380</v>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="5"/>
-    </row>
-    <row r="23" spans="1:12">
-      <c r="H23" s="12" t="s">
+      <c r="I31" s="10"/>
+      <c r="J31" s="11">
+        <f>F31-SUMIF(I2:I30,"已支付",F2:F30)</f>
+        <v>380.00000000000011</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12" hidden="1">
+      <c r="H32" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I23" s="13"/>
-      <c r="J23" s="12">
-        <f>SUMIF(I2:I21,"已支付",F2:F21)</f>
-        <v>387</v>
-      </c>
-      <c r="K23" s="12"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="12">
+        <f>SUMIF(I2:I30,"已支付",F2:F30)</f>
+        <v>512.7399999999999</v>
+      </c>
+      <c r="K32" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L23" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}"/>
+  <autoFilter ref="A1:L32" xr:uid="{D86C6A56-1155-254D-8306-53828F17833A}">
+    <filterColumn colId="8">
+      <filters blank="1">
+        <filter val="已支付"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters blank="1">
+        <filter val="未完成"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="5">
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E1048576">
@@ -1651,7 +2049,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1:I21 J22 I24:I1048576">
+  <conditionalFormatting sqref="J31 I33:I1048576 I1:I30">
     <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
       <formula>"已支付"</formula>
     </cfRule>
@@ -1665,6 +2063,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="67" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/整改与实施计划表.xlsx
+++ b/整改与实施计划表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micropue/Desktop/前后端项目/虎虎校园跑登记系统/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F48BEE3-76C0-184B-B453-4F1B5ACC25ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{598692AA-F0CF-9844-8A54-E8ED70B5FDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{9DB7FF6E-2683-AE40-AAEF-56B36CD941DB}"/>
   </bookViews>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="1:12" ht="51" customHeight="1">
+    <row r="24" spans="1:12" ht="51" hidden="1" customHeight="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1774,9 +1774,11 @@
       <c r="K24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L24" s="8"/>
-    </row>
-    <row r="25" spans="1:12" ht="51" customHeight="1">
+      <c r="L24" s="8">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="51" hidden="1" customHeight="1">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1806,14 +1808,16 @@
         <v>27</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="8"/>
-    </row>
-    <row r="26" spans="1:12" ht="51" customHeight="1">
+      <c r="L25" s="8">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="51" hidden="1" customHeight="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1842,14 +1846,14 @@
         <v>27</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>67</v>
       </c>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" ht="51" customHeight="1">
+    <row r="27" spans="1:12" ht="51" hidden="1" customHeight="1">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1878,14 +1882,14 @@
         <v>27</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>67</v>
       </c>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="1:12" ht="51" customHeight="1">
+    <row r="28" spans="1:12" ht="51" hidden="1" customHeight="1">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1918,9 +1922,11 @@
       <c r="K28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="1:12" ht="85">
+      <c r="L28" s="8">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="85" hidden="1">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1953,9 +1959,11 @@
       <c r="K29" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="L29" s="8">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" hidden="1">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2020,7 +2028,7 @@
       </filters>
     </filterColumn>
     <filterColumn colId="9">
-      <filters blank="1">
+      <filters>
         <filter val="未完成"/>
       </filters>
     </filterColumn>
